--- a/results/0916-all/南岭丘陵山地林农区/tech_selected_summary.xlsx
+++ b/results/0916-all/南岭丘陵山地林农区/tech_selected_summary.xlsx
@@ -298,352 +298,352 @@
     <t>资源县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>技术70</t>
-  </si>
-  <si>
-    <t>技术71</t>
-  </si>
-  <si>
-    <t>技术72</t>
-  </si>
-  <si>
-    <t>技术73</t>
-  </si>
-  <si>
-    <t>技术74</t>
-  </si>
-  <si>
-    <t>技术75</t>
-  </si>
-  <si>
-    <t>技术76</t>
-  </si>
-  <si>
-    <t>技术77</t>
-  </si>
-  <si>
-    <t>技术78</t>
-  </si>
-  <si>
-    <t>技术79</t>
-  </si>
-  <si>
-    <t>技术80</t>
-  </si>
-  <si>
-    <t>技术81</t>
-  </si>
-  <si>
-    <t>技术82</t>
-  </si>
-  <si>
-    <t>技术83</t>
-  </si>
-  <si>
-    <t>技术84</t>
-  </si>
-  <si>
-    <t>技术85</t>
-  </si>
-  <si>
-    <t>技术86</t>
-  </si>
-  <si>
-    <t>技术87</t>
-  </si>
-  <si>
-    <t>技术88</t>
-  </si>
-  <si>
-    <t>技术89</t>
-  </si>
-  <si>
-    <t>技术90</t>
-  </si>
-  <si>
-    <t>技术91</t>
-  </si>
-  <si>
-    <t>技术92</t>
-  </si>
-  <si>
-    <t>技术93</t>
-  </si>
-  <si>
-    <t>技术94</t>
-  </si>
-  <si>
-    <t>技术95</t>
-  </si>
-  <si>
-    <t>技术96</t>
-  </si>
-  <si>
-    <t>技术97</t>
-  </si>
-  <si>
-    <t>技术98</t>
-  </si>
-  <si>
-    <t>技术99</t>
-  </si>
-  <si>
-    <t>技术100</t>
-  </si>
-  <si>
-    <t>技术101</t>
-  </si>
-  <si>
-    <t>技术102</t>
-  </si>
-  <si>
-    <t>技术103</t>
-  </si>
-  <si>
-    <t>技术104</t>
-  </si>
-  <si>
-    <t>技术105</t>
-  </si>
-  <si>
-    <t>技术106</t>
-  </si>
-  <si>
-    <t>技术107</t>
-  </si>
-  <si>
-    <t>技术108</t>
-  </si>
-  <si>
-    <t>技术109</t>
-  </si>
-  <si>
-    <t>技术110</t>
-  </si>
-  <si>
-    <t>技术111</t>
-  </si>
-  <si>
-    <t>技术112</t>
-  </si>
-  <si>
-    <t>技术113</t>
-  </si>
-  <si>
-    <t>技术114</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Tech70</t>
+  </si>
+  <si>
+    <t>Tech71</t>
+  </si>
+  <si>
+    <t>Tech72</t>
+  </si>
+  <si>
+    <t>Tech73</t>
+  </si>
+  <si>
+    <t>Tech74</t>
+  </si>
+  <si>
+    <t>Tech75</t>
+  </si>
+  <si>
+    <t>Tech76</t>
+  </si>
+  <si>
+    <t>Tech77</t>
+  </si>
+  <si>
+    <t>Tech78</t>
+  </si>
+  <si>
+    <t>Tech79</t>
+  </si>
+  <si>
+    <t>Tech80</t>
+  </si>
+  <si>
+    <t>Tech81</t>
+  </si>
+  <si>
+    <t>Tech82</t>
+  </si>
+  <si>
+    <t>Tech83</t>
+  </si>
+  <si>
+    <t>Tech84</t>
+  </si>
+  <si>
+    <t>Tech85</t>
+  </si>
+  <si>
+    <t>Tech86</t>
+  </si>
+  <si>
+    <t>Tech87</t>
+  </si>
+  <si>
+    <t>Tech88</t>
+  </si>
+  <si>
+    <t>Tech89</t>
+  </si>
+  <si>
+    <t>Tech90</t>
+  </si>
+  <si>
+    <t>Tech91</t>
+  </si>
+  <si>
+    <t>Tech92</t>
+  </si>
+  <si>
+    <t>Tech93</t>
+  </si>
+  <si>
+    <t>Tech94</t>
+  </si>
+  <si>
+    <t>Tech95</t>
+  </si>
+  <si>
+    <t>Tech96</t>
+  </si>
+  <si>
+    <t>Tech97</t>
+  </si>
+  <si>
+    <t>Tech98</t>
+  </si>
+  <si>
+    <t>Tech99</t>
+  </si>
+  <si>
+    <t>Tech100</t>
+  </si>
+  <si>
+    <t>Tech101</t>
+  </si>
+  <si>
+    <t>Tech102</t>
+  </si>
+  <si>
+    <t>Tech103</t>
+  </si>
+  <si>
+    <t>Tech104</t>
+  </si>
+  <si>
+    <t>Tech105</t>
+  </si>
+  <si>
+    <t>Tech106</t>
+  </si>
+  <si>
+    <t>Tech107</t>
+  </si>
+  <si>
+    <t>Tech108</t>
+  </si>
+  <si>
+    <t>Tech109</t>
+  </si>
+  <si>
+    <t>Tech110</t>
+  </si>
+  <si>
+    <t>Tech111</t>
+  </si>
+  <si>
+    <t>Tech112</t>
+  </si>
+  <si>
+    <t>Tech113</t>
+  </si>
+  <si>
+    <t>Tech114</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -724,13 +724,13 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 199648601.80</t>
-  </si>
-  <si>
-    <t>总经济成本: 78887.48</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>199648601.80</t>
+  </si>
+  <si>
+    <t>78887.48</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Low protein diet_Pig</t>
@@ -865,7 +865,7 @@
     <t>irrigation (water-saving irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 381541484.93</t>
+    <t>381541484.93</t>
   </si>
   <si>
     <t>Yucca extract_sheep &amp; goat</t>
@@ -874,7 +874,7 @@
     <t>Biochar_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 78601002.21</t>
+    <t>78601002.21</t>
   </si>
   <si>
     <t>Yucca extract_dairy</t>
@@ -898,13 +898,13 @@
     <t>tillage management (zero tillage)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 285684597.35</t>
+    <t>285684597.35</t>
   </si>
   <si>
     <t>nitrification inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 91891243.28</t>
+    <t>91891243.28</t>
   </si>
   <si>
     <t>Zeolite_Poultry</t>
@@ -928,22 +928,22 @@
     <t>irrigation (water-saving irrigation)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 710200753.11</t>
-  </si>
-  <si>
-    <t>总经济成本: 27116707.76</t>
-  </si>
-  <si>
-    <t>总经济成本: 1936618.02</t>
-  </si>
-  <si>
-    <t>总经济成本: 50380648.28</t>
-  </si>
-  <si>
-    <t>总经济成本: 223187.26</t>
-  </si>
-  <si>
-    <t>总经济成本: 294760255.47</t>
+    <t>710200753.11</t>
+  </si>
+  <si>
+    <t>27116707.76</t>
+  </si>
+  <si>
+    <t>1936618.02</t>
+  </si>
+  <si>
+    <t>50380648.28</t>
+  </si>
+  <si>
+    <t>223187.26</t>
+  </si>
+  <si>
+    <t>294760255.47</t>
   </si>
   <si>
     <t>Probiotics_pig</t>
@@ -955,7 +955,7 @@
     <t>manure（high）≥70%_rice</t>
   </si>
   <si>
-    <t>总经济成本: 957998534.79</t>
+    <t>957998534.79</t>
   </si>
   <si>
     <t>EEF(NI)_wheat</t>
@@ -973,13 +973,13 @@
     <t>4R(Right rate)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 127217437.53</t>
-  </si>
-  <si>
-    <t>总经济成本: 8866123.06</t>
-  </si>
-  <si>
-    <t>总经济成本: 144054642.68</t>
+    <t>127217437.53</t>
+  </si>
+  <si>
+    <t>8866123.06</t>
+  </si>
+  <si>
+    <t>144054642.68</t>
   </si>
   <si>
     <t>Slatted floor vs deep litter_pig</t>
@@ -1015,10 +1015,10 @@
     <t>tillage management (zero tillage)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 220637293.41</t>
-  </si>
-  <si>
-    <t>总经济成本: 67782294.83</t>
+    <t>220637293.41</t>
+  </si>
+  <si>
+    <t>67782294.83</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
@@ -1039,34 +1039,34 @@
     <t>residue rerention_maize</t>
   </si>
   <si>
-    <t>总经济成本: 294821699.83</t>
-  </si>
-  <si>
-    <t>总经济成本: 35359153.81</t>
-  </si>
-  <si>
-    <t>总经济成本: 262492423.36</t>
-  </si>
-  <si>
-    <t>总经济成本: 440737530.08</t>
-  </si>
-  <si>
-    <t>总经济成本: 574831237.34</t>
+    <t>294821699.83</t>
+  </si>
+  <si>
+    <t>35359153.81</t>
+  </si>
+  <si>
+    <t>262492423.36</t>
+  </si>
+  <si>
+    <t>440737530.08</t>
+  </si>
+  <si>
+    <t>574831237.34</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 77390356.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 42738177.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 49596022.81</t>
-  </si>
-  <si>
-    <t>总经济成本: 283886.03</t>
+    <t>77390356.89</t>
+  </si>
+  <si>
+    <t>42738177.25</t>
+  </si>
+  <si>
+    <t>49596022.81</t>
+  </si>
+  <si>
+    <t>283886.03</t>
   </si>
   <si>
     <t>Low protein diet_dairy</t>
@@ -1123,19 +1123,19 @@
     <t>4R(Right type)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 1250465327.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 465938832.68</t>
-  </si>
-  <si>
-    <t>总经济成本: 24555179.57</t>
-  </si>
-  <si>
-    <t>总经济成本: 2535632.23</t>
-  </si>
-  <si>
-    <t>总经济成本: 1565976.38</t>
+    <t>1250465327.15</t>
+  </si>
+  <si>
+    <t>465938832.68</t>
+  </si>
+  <si>
+    <t>24555179.57</t>
+  </si>
+  <si>
+    <t>2535632.23</t>
+  </si>
+  <si>
+    <t>1565976.38</t>
   </si>
   <si>
     <t>Frequent removal_dairy</t>
@@ -1144,52 +1144,52 @@
     <t>Urease Inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 937021308.87</t>
-  </si>
-  <si>
-    <t>总经济成本: 70450588.50</t>
+    <t>937021308.87</t>
+  </si>
+  <si>
+    <t>70450588.50</t>
   </si>
   <si>
     <t>Urease Inhibitor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 515203405.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 166767910.61</t>
-  </si>
-  <si>
-    <t>总经济成本: 1639089.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 17250427.86</t>
-  </si>
-  <si>
-    <t>总经济成本: 154740286.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 184875294.87</t>
-  </si>
-  <si>
-    <t>总经济成本: 121049363.92</t>
-  </si>
-  <si>
-    <t>总经济成本: 1814529.64</t>
-  </si>
-  <si>
-    <t>总经济成本: 299350.70</t>
-  </si>
-  <si>
-    <t>总经济成本: 609486.99</t>
-  </si>
-  <si>
-    <t>总经济成本: 125114069.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 154821953.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 18443190.82</t>
+    <t>515203405.10</t>
+  </si>
+  <si>
+    <t>166767910.61</t>
+  </si>
+  <si>
+    <t>1639089.25</t>
+  </si>
+  <si>
+    <t>17250427.86</t>
+  </si>
+  <si>
+    <t>154740286.59</t>
+  </si>
+  <si>
+    <t>184875294.87</t>
+  </si>
+  <si>
+    <t>121049363.92</t>
+  </si>
+  <si>
+    <t>1814529.64</t>
+  </si>
+  <si>
+    <t>299350.70</t>
+  </si>
+  <si>
+    <t>609486.99</t>
+  </si>
+  <si>
+    <t>125114069.84</t>
+  </si>
+  <si>
+    <t>154821953.00</t>
+  </si>
+  <si>
+    <t>18443190.82</t>
   </si>
   <si>
     <t>Chemical amendments_pig</t>
@@ -1198,64 +1198,64 @@
     <t>Mixture additives _pig</t>
   </si>
   <si>
-    <t>总经济成本: 313837629.92</t>
-  </si>
-  <si>
-    <t>总经济成本: 365594678.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 1312093.30</t>
-  </si>
-  <si>
-    <t>总经济成本: 463372228.86</t>
-  </si>
-  <si>
-    <t>总经济成本: 681673.43</t>
-  </si>
-  <si>
-    <t>总经济成本: 180699221.39</t>
-  </si>
-  <si>
-    <t>总经济成本: 102304103.42</t>
-  </si>
-  <si>
-    <t>总经济成本: 4322730.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 702026581.22</t>
-  </si>
-  <si>
-    <t>总经济成本: 5223858.26</t>
-  </si>
-  <si>
-    <t>总经济成本: 76165713.40</t>
-  </si>
-  <si>
-    <t>总经济成本: 494019990.80</t>
-  </si>
-  <si>
-    <t>总经济成本: 17517655.48</t>
-  </si>
-  <si>
-    <t>总经济成本: 119268285.13</t>
+    <t>313837629.92</t>
+  </si>
+  <si>
+    <t>365594678.60</t>
+  </si>
+  <si>
+    <t>1312093.30</t>
+  </si>
+  <si>
+    <t>463372228.86</t>
+  </si>
+  <si>
+    <t>681673.43</t>
+  </si>
+  <si>
+    <t>180699221.39</t>
+  </si>
+  <si>
+    <t>102304103.42</t>
+  </si>
+  <si>
+    <t>4322730.15</t>
+  </si>
+  <si>
+    <t>702026581.22</t>
+  </si>
+  <si>
+    <t>5223858.26</t>
+  </si>
+  <si>
+    <t>76165713.40</t>
+  </si>
+  <si>
+    <t>494019990.80</t>
+  </si>
+  <si>
+    <t>17517655.48</t>
+  </si>
+  <si>
+    <t>119268285.13</t>
   </si>
   <si>
     <t>4R(Right time)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 409522713.16</t>
-  </si>
-  <si>
-    <t>总经济成本: 1920001.56</t>
-  </si>
-  <si>
-    <t>总经济成本: 3629121.56</t>
-  </si>
-  <si>
-    <t>总经济成本: 56703860.94</t>
-  </si>
-  <si>
-    <t>总经济成本: 4299560.53</t>
+    <t>409522713.16</t>
+  </si>
+  <si>
+    <t>1920001.56</t>
+  </si>
+  <si>
+    <t>3629121.56</t>
+  </si>
+  <si>
+    <t>56703860.94</t>
+  </si>
+  <si>
+    <t>4299560.53</t>
   </si>
 </sst>
 </file>
